--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-23.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>1.91</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>1.82</v>
       </c>
       <c r="H3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>1.67</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>1.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.86</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>2.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.19</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="n">
-        <v>29</v>
+        <v>4.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.06</v>
+        <v>2.1</v>
       </c>
       <c r="I8" t="n">
-        <v>7.4</v>
+        <v>2.56</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>610</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I9" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
         <v>4.4</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>2.42</v>
+        <v>4.9</v>
       </c>
       <c r="K15" t="n">
-        <v>820</v>
+        <v>7.4</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>2.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>1.87</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>580</v>
+        <v>5.3</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G17" t="n">
         <v>2.34</v>
       </c>
       <c r="H17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J17" t="n">
         <v>3.55</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.09</v>
+        <v>2.04</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H18" t="n">
-        <v>1.87</v>
+        <v>3.85</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.09</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>1.78</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -6215,22 +6215,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.24</v>
+        <v>2.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="R23" t="n">
-        <v>1.05</v>
+        <v>1.58</v>
       </c>
       <c r="S23" t="n">
-        <v>1.12</v>
+        <v>1.92</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -6239,10 +6239,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -6445,230 +6445,230 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="J24" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M24" t="n">
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P24" t="n">
-        <v>1.25</v>
+        <v>2.44</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="R24" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="S24" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BB24" t="n">
         <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE24" t="n">
         <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.09</v>
+        <v>1.58</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>1.71</v>
       </c>
       <c r="H26" t="n">
-        <v>1.09</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>100</v>
+        <v>7.4</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="G27" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="H27" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="I27" t="n">
-        <v>100</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
-        <v>2.14</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>3.8</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7237,10 +7237,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -7461,19 +7461,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.3</v>
+        <v>2.76</v>
       </c>
       <c r="G28" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="H28" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="I28" t="n">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="J28" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K28" t="n">
         <v>3.9</v>
@@ -7491,10 +7491,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J29" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -7745,10 +7745,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>1.95</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="J30" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="K30" t="n">
-        <v>720</v>
+        <v>4.8</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -7999,10 +7999,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -8223,22 +8223,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>2.22</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="I31" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J31" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>2.12</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G32" t="n">
-        <v>5.5</v>
+        <v>2.36</v>
       </c>
       <c r="H32" t="n">
-        <v>1.27</v>
+        <v>3.4</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
-        <v>1.22</v>
+        <v>2.98</v>
       </c>
       <c r="K32" t="n">
-        <v>29</v>
+        <v>4.4</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -8731,230 +8731,230 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>2.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -8985,19 +8985,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H34" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J34" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K34" t="n">
         <v>770</v>
@@ -9015,10 +9015,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -9239,10 +9239,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G35" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H35" t="n">
         <v>2.36</v>
@@ -9281,10 +9281,10 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U35" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -9293,109 +9293,109 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA35" t="n">
         <v>34</v>
       </c>
-      <c r="Y35" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1000</v>
-      </c>
       <c r="AB35" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE35" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AF35" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AG35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH35" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH35" t="n">
-        <v>15</v>
-      </c>
       <c r="AI35" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK35" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN35" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AO35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ35" t="n">
         <v>13</v>
       </c>
       <c r="AR35" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AS35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT35" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AU35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV35" t="n">
         <v>10.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AY35" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA35" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BB35" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE35" t="n">
         <v>40</v>
       </c>
-      <c r="BC35" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>38</v>
-      </c>
       <c r="BF35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG35" t="n">
         <v>11</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -9493,28 +9493,28 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="G36" t="n">
-        <v>1000</v>
+        <v>1.93</v>
       </c>
       <c r="H36" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -9523,10 +9523,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.05</v>
+        <v>1.73</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -9747,22 +9747,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="G37" t="n">
-        <v>1000</v>
+        <v>1.38</v>
       </c>
       <c r="H37" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="I37" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="J37" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="K37" t="n">
-        <v>910</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -9777,10 +9777,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -10001,58 +10001,58 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="G38" t="n">
-        <v>970</v>
+        <v>1.76</v>
       </c>
       <c r="H38" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I38" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="J38" t="n">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="K38" t="n">
-        <v>770</v>
+        <v>4.4</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N38" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="O38" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="P38" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="R38" t="n">
         <v>1.12</v>
       </c>
       <c r="S38" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="V38" t="n">
         <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -10070,7 +10070,7 @@
         <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD38" t="n">
         <v>1000</v>
@@ -10079,7 +10079,7 @@
         <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG38" t="n">
         <v>1000</v>
@@ -10091,7 +10091,7 @@
         <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -10255,64 +10255,64 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="G39" t="n">
-        <v>970</v>
+        <v>3.3</v>
       </c>
       <c r="H39" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>970</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
-        <v>1.02</v>
+        <v>2.6</v>
       </c>
       <c r="K39" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N39" t="n">
         <v>1.25</v>
       </c>
       <c r="O39" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="P39" t="n">
         <v>1.24</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.02</v>
+        <v>2.34</v>
       </c>
       <c r="R39" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S39" t="n">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z39" t="n">
         <v>1000</v>
@@ -10324,7 +10324,7 @@
         <v>1000</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD39" t="n">
         <v>1000</v>
@@ -10366,7 +10366,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -10509,94 +10509,94 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="G40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X40" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z40" t="n">
         <v>970</v>
       </c>
-      <c r="H40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I40" t="n">
+      <c r="AA40" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC40" t="n">
         <v>970</v>
       </c>
-      <c r="J40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K40" t="n">
-        <v>110</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1000</v>
-      </c>
       <c r="AD40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE40" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF40" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG40" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH40" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI40" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ40" t="n">
         <v>1000</v>
@@ -10608,13 +10608,13 @@
         <v>1000</v>
       </c>
       <c r="AM40" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN40" t="n">
         <v>1000</v>
       </c>
       <c r="AO40" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP40" t="n">
         <v>1.01</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -10763,166 +10763,166 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="G41" t="n">
-        <v>970</v>
+        <v>3.2</v>
       </c>
       <c r="H41" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>970</v>
+        <v>3.45</v>
       </c>
       <c r="J41" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="K41" t="n">
-        <v>110</v>
+        <v>3.25</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="N41" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="O41" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="P41" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="R41" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S41" t="n">
         <v>1.02</v>
       </c>
       <c r="T41" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U41" t="n">
         <v>1.01</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W41" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="X41" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA41" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB41" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF41" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG41" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH41" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI41" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK41" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL41" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM41" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN41" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO41" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE41" t="n">
         <v>1.01</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -11017,22 +11017,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="G42" t="n">
         <v>2.18</v>
       </c>
       <c r="H42" t="n">
-        <v>1.85</v>
+        <v>3.85</v>
       </c>
       <c r="I42" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
-        <v>1.86</v>
+        <v>3.35</v>
       </c>
       <c r="K42" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -11047,10 +11047,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -11274,19 +11274,19 @@
         <v>3.95</v>
       </c>
       <c r="G43" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="H43" t="n">
-        <v>1.09</v>
+        <v>2.02</v>
       </c>
       <c r="I43" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="J43" t="n">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="K43" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -11301,10 +11301,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -11525,22 +11525,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="G44" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="H44" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I44" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J44" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K44" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -11555,10 +11555,10 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -11779,230 +11779,230 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q45" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q45" t="n">
-        <v>1.01</v>
-      </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ45" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -12033,22 +12033,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
         <v>2.18</v>
       </c>
       <c r="H46" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="I46" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J46" t="n">
-        <v>1.86</v>
+        <v>3.35</v>
       </c>
       <c r="K46" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -12287,19 +12287,19 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="G47" t="n">
         <v>1000</v>
       </c>
       <c r="H47" t="n">
-        <v>1.09</v>
+        <v>1.84</v>
       </c>
       <c r="I47" t="n">
         <v>1000</v>
       </c>
       <c r="J47" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="K47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -12541,22 +12541,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="G48" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="H48" t="n">
-        <v>1.09</v>
+        <v>1.93</v>
       </c>
       <c r="I48" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
-        <v>1.09</v>
+        <v>3.8</v>
       </c>
       <c r="K48" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -12807,7 +12807,7 @@
         <v>7</v>
       </c>
       <c r="J49" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K49" t="n">
         <v>4.5</v>
@@ -12840,7 +12840,7 @@
         <v>1.93</v>
       </c>
       <c r="U49" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -12849,10 +12849,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y49" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z49" t="n">
         <v>240</v>
@@ -12861,100 +12861,100 @@
         <v>900</v>
       </c>
       <c r="AB49" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC49" t="n">
         <v>9.6</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AD49" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF49" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AG49" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL49" t="n">
         <v>36</v>
       </c>
-      <c r="AE49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>80</v>
-      </c>
       <c r="AM49" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN49" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO49" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP49" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ49" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AR49" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS49" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT49" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU49" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV49" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AW49" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY49" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AZ49" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BA49" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB49" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC49" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BD49" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE49" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF49" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG49" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH49" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -13049,230 +13049,230 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P50" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ50" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -13303,22 +13303,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="G51" t="n">
-        <v>520</v>
+        <v>1.9</v>
       </c>
       <c r="H51" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="I51" t="n">
-        <v>660</v>
+        <v>6.2</v>
       </c>
       <c r="J51" t="n">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="K51" t="n">
-        <v>410</v>
+        <v>4.4</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -13333,10 +13333,10 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -13557,22 +13557,22 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="G52" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H52" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J52" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K52" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -13587,10 +13587,10 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -13811,19 +13811,19 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="G53" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="H53" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="I53" t="n">
         <v>1000</v>
       </c>
       <c r="J53" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="K53" t="n">
         <v>1000</v>
@@ -13841,10 +13841,10 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.06</v>
+        <v>1.98</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -14065,19 +14065,19 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="G54" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H54" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="I54" t="n">
         <v>1000</v>
       </c>
       <c r="J54" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="K54" t="n">
         <v>1000</v>
@@ -14098,7 +14098,7 @@
         <v>1.24</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -14319,22 +14319,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="G55" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H55" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="I55" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="K55" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L55" t="n">
         <v>1.01</v>
@@ -14343,22 +14343,22 @@
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="O55" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P55" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R55" t="n">
         <v>1.01</v>
       </c>
       <c r="S55" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="T55" t="n">
         <v>1.01</v>
@@ -14367,10 +14367,10 @@
         <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="W55" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -14573,22 +14573,22 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="G56" t="n">
-        <v>970</v>
+        <v>1.56</v>
       </c>
       <c r="H56" t="n">
-        <v>1.09</v>
+        <v>8.4</v>
       </c>
       <c r="I56" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="J56" t="n">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="K56" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
@@ -14597,52 +14597,52 @@
         <v>1.06</v>
       </c>
       <c r="N56" t="n">
-        <v>1.25</v>
+        <v>2.92</v>
       </c>
       <c r="O56" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P56" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.37</v>
+        <v>2.12</v>
       </c>
       <c r="R56" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="S56" t="n">
-        <v>1.37</v>
+        <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U56" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="V56" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W56" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="X56" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y56" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z56" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA56" t="n">
         <v>1000</v>
       </c>
       <c r="AB56" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC56" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD56" t="n">
         <v>1000</v>
@@ -14654,7 +14654,7 @@
         <v>1000</v>
       </c>
       <c r="AG56" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH56" t="n">
         <v>1000</v>
@@ -14663,13 +14663,13 @@
         <v>1000</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK56" t="n">
         <v>1000</v>
       </c>
       <c r="AL56" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM56" t="n">
         <v>1000</v>
@@ -14681,58 +14681,58 @@
         <v>1000</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG56" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BH56" t="n">
         <v>1000</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -14827,19 +14827,19 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="G57" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H57" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="I57" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="J57" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="K57" t="n">
         <v>1000</v>
@@ -14857,10 +14857,10 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -15081,19 +15081,19 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="G58" t="n">
-        <v>1000</v>
+        <v>2.02</v>
       </c>
       <c r="H58" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="I58" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J58" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="K58" t="n">
         <v>380</v>
@@ -15111,10 +15111,10 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -15335,22 +15335,22 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="G59" t="n">
-        <v>1000</v>
+        <v>1.74</v>
       </c>
       <c r="H59" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I59" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J59" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="K59" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -15365,10 +15365,10 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>
@@ -15589,22 +15589,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.09</v>
+        <v>2.28</v>
       </c>
       <c r="G60" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H60" t="n">
-        <v>1.09</v>
+        <v>3.5</v>
       </c>
       <c r="I60" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
-        <v>1.09</v>
+        <v>3.1</v>
       </c>
       <c r="K60" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -15619,10 +15619,10 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-21 02:14:04</t>
+          <t>2026-05-21 04:33:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-23.xlsx
@@ -860,7 +860,7 @@
         <v>3.4</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H2" t="n">
         <v>2.04</v>
@@ -896,7 +896,7 @@
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
         <v>1.61</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>2.04</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
         <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.28</v>
@@ -1150,7 +1150,7 @@
         <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
         <v>1.75</v>
@@ -1159,7 +1159,7 @@
         <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W3" t="n">
         <v>1.97</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -1530,65 +1530,65 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
         <v>2.1</v>
@@ -1658,13 +1658,13 @@
         <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T5" t="n">
         <v>1.85</v>
       </c>
       <c r="U5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V5" t="n">
         <v>1.34</v>
@@ -1688,7 +1688,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
         <v>16.5</v>
@@ -1709,7 +1709,7 @@
         <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1721,7 +1721,7 @@
         <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO5" t="n">
         <v>55</v>
@@ -1736,10 +1736,10 @@
         <v>20</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5" t="n">
         <v>7</v>
@@ -1748,7 +1748,7 @@
         <v>13.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
         <v>11.5</v>
@@ -1763,7 +1763,7 @@
         <v>42</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1772,13 +1772,13 @@
         <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF5" t="n">
         <v>16.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH5" t="n">
         <v>3.35</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -1873,70 +1873,70 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G6" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
         <v>1.66</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
         <v>2.62</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W6" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="X6" t="n">
         <v>25</v>
       </c>
       <c r="Y6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z6" t="n">
         <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB6" t="n">
         <v>11.5</v>
@@ -1945,28 +1945,28 @@
         <v>12.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK6" t="n">
         <v>21</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>20</v>
       </c>
       <c r="AL6" t="n">
         <v>36</v>
@@ -1978,7 +1978,7 @@
         <v>11</v>
       </c>
       <c r="AO6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP6" t="n">
         <v>14.5</v>
@@ -2005,7 +2005,7 @@
         <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY6" t="n">
         <v>7.2</v>
@@ -2038,19 +2038,19 @@
         <v>3.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BN6" t="n">
         <v>4.6</v>
@@ -2062,31 +2062,31 @@
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,16 @@
         <v>1.48</v>
       </c>
       <c r="G7" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="I7" t="n">
         <v>7.4</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="K7" t="n">
         <v>5.2</v>
@@ -2178,7 +2178,7 @@
         <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -2420,13 +2420,13 @@
         <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="T8" t="n">
         <v>1.86</v>
       </c>
       <c r="U8" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="V8" t="n">
         <v>3.2</v>
@@ -2462,7 +2462,7 @@
         <v>80</v>
       </c>
       <c r="AG8" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AH8" t="n">
         <v>27</v>
@@ -2489,10 +2489,10 @@
         <v>970</v>
       </c>
       <c r="AP8" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AR8" t="n">
         <v>7</v>
@@ -2501,43 +2501,43 @@
         <v>8.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AU8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV8" t="n">
         <v>4.8</v>
       </c>
-      <c r="AV8" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AW8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AY8" t="n">
         <v>6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="BG8" t="n">
         <v>4</v>
@@ -2546,65 +2546,65 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H9" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="I9" t="n">
         <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2659,7 +2659,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1.08</v>
@@ -2671,13 +2671,13 @@
         <v>1.24</v>
       </c>
       <c r="R9" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="S9" t="n">
         <v>1.53</v>
       </c>
       <c r="T9" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="U9" t="n">
         <v>1.45</v>
@@ -2686,7 +2686,7 @@
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2737,82 +2737,82 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BB9" t="n">
         <v>6</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BD9" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF9" t="n">
         <v>1.76</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
@@ -2824,41 +2824,41 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -2895,13 +2895,13 @@
         <v>1.82</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
         <v>4.8</v>
@@ -2910,34 +2910,34 @@
         <v>1.26</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
         <v>4.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S10" t="n">
         <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
         <v>2.22</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -3146,10 +3146,10 @@
         <v>1.2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I11" t="n">
         <v>22</v>
@@ -3158,7 +3158,7 @@
         <v>5.9</v>
       </c>
       <c r="K11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3176,16 +3176,16 @@
         <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="R11" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="T11" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
         <v>1.7</v>
@@ -3308,55 +3308,55 @@
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>2.68</v>
       </c>
       <c r="G12" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H12" t="n">
         <v>2.86</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J12" t="n">
         <v>3.05</v>
@@ -3436,7 +3436,7 @@
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
         <v>1.92</v>
@@ -3445,10 +3445,10 @@
         <v>1.92</v>
       </c>
       <c r="V12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W12" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="X12" t="n">
         <v>12</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -4070,65 +4070,65 @@
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -4324,65 +4324,65 @@
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -4578,65 +4578,65 @@
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -4667,25 +4667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I17" t="n">
         <v>5.3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
         <v>4.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -4712,7 +4712,7 @@
         <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V17" t="n">
         <v>1.23</v>
@@ -4739,7 +4739,7 @@
         <v>9</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>80</v>
@@ -4778,10 +4778,10 @@
         <v>14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>4.3</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS17" t="n">
         <v>5.2</v>
@@ -4793,10 +4793,10 @@
         <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>15.5</v>
+        <v>4.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX17" t="n">
         <v>9.800000000000001</v>
@@ -4808,7 +4808,7 @@
         <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB17" t="n">
         <v>16</v>
@@ -4820,7 +4820,7 @@
         <v>4.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF17" t="n">
         <v>8.199999999999999</v>
@@ -4838,13 +4838,13 @@
         <v>10</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN17" t="n">
         <v>4.4</v>
@@ -4853,44 +4853,44 @@
         <v>3.55</v>
       </c>
       <c r="BP17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
         <v>4.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BN18" t="n">
         <v>5.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
         <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>1.05</v>
+        <v>1.44</v>
       </c>
       <c r="T19" t="n">
         <v>1.11</v>
@@ -5340,65 +5340,65 @@
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G20" t="n">
         <v>1.77</v>
       </c>
       <c r="H20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
         <v>5.6</v>
       </c>
       <c r="J20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5459,16 +5459,16 @@
         <v>1.21</v>
       </c>
       <c r="P20" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="R20" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T20" t="n">
         <v>1.67</v>
@@ -5477,10 +5477,10 @@
         <v>2.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W20" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X20" t="n">
         <v>27</v>
@@ -5531,34 +5531,34 @@
         <v>80</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO20" t="n">
         <v>60</v>
       </c>
       <c r="AP20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV20" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS20" t="n">
+      <c r="AW20" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4.7</v>
       </c>
       <c r="AX20" t="n">
         <v>10.5</v>
@@ -5570,25 +5570,25 @@
         <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF20" t="n">
         <v>6.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5707,7 @@
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1</v>
+        <v>1.94</v>
       </c>
       <c r="O21" t="n">
         <v>1.26</v>
@@ -5722,7 +5722,7 @@
         <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.58</v>
+        <v>1.74</v>
       </c>
       <c r="T21" t="n">
         <v>1.66</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -6102,65 +6102,65 @@
         <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
         <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -6356,65 +6356,65 @@
         <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23" t="n">
         <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
         <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
         <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6487,7 @@
         <v>2.08</v>
       </c>
       <c r="T24" t="n">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="U24" t="n">
         <v>1.11</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -6864,65 +6864,65 @@
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -7118,65 +7118,65 @@
         <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26" t="n">
         <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26" t="n">
         <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26" t="n">
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -7216,10 +7216,10 @@
         <v>3.85</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J27" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K27" t="n">
         <v>4.7</v>
@@ -7372,65 +7372,65 @@
         <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27" t="n">
         <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN27" t="n">
         <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT27" t="n">
         <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -7626,65 +7626,65 @@
         <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ28" t="n">
         <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN28" t="n">
         <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT28" t="n">
         <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -7880,65 +7880,65 @@
         <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29" t="n">
         <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN29" t="n">
         <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP29" t="n">
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT29" t="n">
         <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29" t="n">
         <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -8134,65 +8134,65 @@
         <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ30" t="n">
         <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN30" t="n">
         <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT30" t="n">
         <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G31" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H31" t="n">
         <v>1.93</v>
@@ -8238,10 +8238,10 @@
         <v>3.85</v>
       </c>
       <c r="K31" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
         <v>1.06</v>
@@ -8250,7 +8250,7 @@
         <v>3.6</v>
       </c>
       <c r="O31" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P31" t="n">
         <v>1.91</v>
@@ -8280,7 +8280,7 @@
         <v>16</v>
       </c>
       <c r="Y31" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z31" t="n">
         <v>970</v>
@@ -8349,13 +8349,13 @@
         <v>6.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW31" t="n">
         <v>17</v>
       </c>
       <c r="AX31" t="n">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="AY31" t="n">
         <v>13</v>
@@ -8373,7 +8373,7 @@
         <v>40</v>
       </c>
       <c r="BD31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE31" t="n">
         <v>6</v>
@@ -8436,7 +8436,7 @@
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
         <v>2.8</v>
       </c>
       <c r="I32" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J32" t="n">
         <v>3.55</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -8734,19 +8734,19 @@
         <v>1.52</v>
       </c>
       <c r="G33" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H33" t="n">
         <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J33" t="n">
         <v>4.5</v>
       </c>
       <c r="K33" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L33" t="n">
         <v>1.31</v>
@@ -8773,7 +8773,7 @@
         <v>2.6</v>
       </c>
       <c r="T33" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U33" t="n">
         <v>2.08</v>
@@ -8782,7 +8782,7 @@
         <v>1.16</v>
       </c>
       <c r="W33" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X33" t="n">
         <v>28</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -8988,19 +8988,19 @@
         <v>2.16</v>
       </c>
       <c r="G34" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H34" t="n">
         <v>3.15</v>
       </c>
       <c r="I34" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J34" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -9018,7 +9018,7 @@
         <v>2.14</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R34" t="n">
         <v>1.45</v>
@@ -9033,7 +9033,7 @@
         <v>2.28</v>
       </c>
       <c r="V34" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W34" t="n">
         <v>1.74</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
         <v>1.81</v>
       </c>
       <c r="I35" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J35" t="n">
         <v>3.85</v>
@@ -9272,7 +9272,7 @@
         <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="R35" t="n">
         <v>1.48</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -9493,22 +9493,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G36" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="H36" t="n">
         <v>2.62</v>
       </c>
       <c r="I36" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="J36" t="n">
         <v>3.65</v>
       </c>
       <c r="K36" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -9532,7 +9532,7 @@
         <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="T36" t="n">
         <v>1.59</v>
@@ -9541,10 +9541,10 @@
         <v>2.3</v>
       </c>
       <c r="V36" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X36" t="n">
         <v>970</v>
@@ -9553,7 +9553,7 @@
         <v>17.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA36" t="n">
         <v>55</v>
@@ -9586,19 +9586,19 @@
         <v>38</v>
       </c>
       <c r="AK36" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL36" t="n">
         <v>38</v>
       </c>
       <c r="AM36" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN36" t="n">
         <v>26</v>
       </c>
       <c r="AO36" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP36" t="n">
         <v>12</v>
@@ -9607,28 +9607,28 @@
         <v>11.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS36" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT36" t="n">
         <v>10.5</v>
       </c>
       <c r="AU36" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV36" t="n">
         <v>11</v>
       </c>
       <c r="AW36" t="n">
-        <v>22</v>
+        <v>6.4</v>
       </c>
       <c r="AX36" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AY36" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AZ36" t="n">
         <v>13.5</v>
@@ -9640,13 +9640,13 @@
         <v>28</v>
       </c>
       <c r="BC36" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD36" t="n">
         <v>27</v>
       </c>
       <c r="BE36" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF36" t="n">
         <v>13</v>
@@ -9658,65 +9658,65 @@
         <v>1000</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ36" t="n">
         <v>1000</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN36" t="n">
         <v>1000</v>
       </c>
       <c r="BO36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP36" t="n">
         <v>1000</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR36" t="n">
         <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT36" t="n">
         <v>1000</v>
       </c>
       <c r="BU36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV36" t="n">
         <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX36" t="n">
         <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ36" t="n">
         <v>1000</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -9918,13 +9918,13 @@
         <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BN37" t="n">
         <v>4</v>
@@ -9942,35 +9942,35 @@
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT37" t="n">
         <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV37" t="n">
         <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -10010,13 +10010,13 @@
         <v>2.1</v>
       </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="J38" t="n">
         <v>3.05</v>
       </c>
       <c r="K38" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -10034,7 +10034,7 @@
         <v>1.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R38" t="n">
         <v>1.19</v>
@@ -10049,7 +10049,7 @@
         <v>1.11</v>
       </c>
       <c r="V38" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="W38" t="n">
         <v>1.25</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -10321,7 +10321,7 @@
         <v>55</v>
       </c>
       <c r="AB39" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC39" t="n">
         <v>9.800000000000001</v>
@@ -10405,7 +10405,7 @@
         <v>18</v>
       </c>
       <c r="BD39" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE39" t="n">
         <v>50</v>
@@ -10420,65 +10420,65 @@
         <v>1000</v>
       </c>
       <c r="BI39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ39" t="n">
         <v>1000</v>
       </c>
       <c r="BK39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN39" t="n">
         <v>1000</v>
       </c>
       <c r="BO39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP39" t="n">
         <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR39" t="n">
         <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT39" t="n">
         <v>1000</v>
       </c>
       <c r="BU39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV39" t="n">
         <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ39" t="n">
         <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -10509,10 +10509,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="G40" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H40" t="n">
         <v>3.7</v>
@@ -10521,7 +10521,7 @@
         <v>4.2</v>
       </c>
       <c r="J40" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K40" t="n">
         <v>3.9</v>
@@ -10533,13 +10533,13 @@
         <v>1.06</v>
       </c>
       <c r="N40" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O40" t="n">
         <v>1.29</v>
       </c>
       <c r="P40" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q40" t="n">
         <v>1.86</v>
@@ -10551,13 +10551,13 @@
         <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U40" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V40" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W40" t="n">
         <v>1.86</v>
@@ -10674,65 +10674,65 @@
         <v>1000</v>
       </c>
       <c r="BI40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ40" t="n">
         <v>1000</v>
       </c>
       <c r="BK40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN40" t="n">
         <v>1000</v>
       </c>
       <c r="BO40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP40" t="n">
         <v>1000</v>
       </c>
       <c r="BQ40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR40" t="n">
         <v>1000</v>
       </c>
       <c r="BS40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT40" t="n">
         <v>1000</v>
       </c>
       <c r="BU40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV40" t="n">
         <v>1000</v>
       </c>
       <c r="BW40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX40" t="n">
         <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ40" t="n">
         <v>1000</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G41" t="n">
         <v>2.32</v>
@@ -10772,7 +10772,7 @@
         <v>3.5</v>
       </c>
       <c r="I41" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J41" t="n">
         <v>3.55</v>
@@ -10781,28 +10781,28 @@
         <v>3.75</v>
       </c>
       <c r="L41" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M41" t="n">
         <v>1.07</v>
       </c>
       <c r="N41" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>1.32</v>
       </c>
       <c r="P41" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R41" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S41" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T41" t="n">
         <v>1.77</v>
@@ -10820,34 +10820,34 @@
         <v>17.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA41" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AB41" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC41" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD41" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE41" t="n">
         <v>55</v>
       </c>
       <c r="AF41" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AG41" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI41" t="n">
         <v>55</v>
@@ -10865,10 +10865,10 @@
         <v>120</v>
       </c>
       <c r="AN41" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AO41" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AP41" t="n">
         <v>12.5</v>
@@ -10880,7 +10880,7 @@
         <v>21</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT41" t="n">
         <v>8.800000000000001</v>
@@ -10892,19 +10892,19 @@
         <v>12.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AX41" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY41" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ41" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BB41" t="n">
         <v>21</v>
@@ -10913,80 +10913,80 @@
         <v>17.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BF41" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BH41" t="n">
         <v>1000</v>
       </c>
       <c r="BI41" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BJ41" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK41" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BN41" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO41" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP41" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="BR41" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BT41" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU41" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV41" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BZ41" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -11020,58 +11020,58 @@
         <v>2.04</v>
       </c>
       <c r="G42" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H42" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I42" t="n">
         <v>4.6</v>
       </c>
       <c r="J42" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K42" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N42" t="n">
         <v>3.2</v>
       </c>
       <c r="O42" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P42" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R42" t="n">
         <v>1.28</v>
       </c>
       <c r="S42" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T42" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U42" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V42" t="n">
         <v>1.27</v>
       </c>
       <c r="W42" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="X42" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y42" t="n">
         <v>16.5</v>
@@ -11086,7 +11086,7 @@
         <v>9.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD42" t="n">
         <v>22</v>
@@ -11098,7 +11098,7 @@
         <v>14.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH42" t="n">
         <v>21</v>
@@ -11110,7 +11110,7 @@
         <v>30</v>
       </c>
       <c r="AK42" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL42" t="n">
         <v>55</v>
@@ -11128,37 +11128,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ42" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT42" t="n">
         <v>7</v>
       </c>
       <c r="AU42" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX42" t="n">
         <v>10</v>
       </c>
       <c r="AY42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ42" t="n">
         <v>17.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB42" t="n">
         <v>21</v>
@@ -11167,80 +11167,80 @@
         <v>20</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF42" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BH42" t="n">
         <v>1000</v>
       </c>
       <c r="BI42" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BJ42" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK42" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BN42" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO42" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP42" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BR42" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS42" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="BT42" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU42" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV42" t="n">
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BZ42" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA42" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -11690,65 +11690,65 @@
         <v>1000</v>
       </c>
       <c r="BI44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ44" t="n">
         <v>1000</v>
       </c>
       <c r="BK44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL44" t="n">
         <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN44" t="n">
         <v>1000</v>
       </c>
       <c r="BO44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP44" t="n">
         <v>1000</v>
       </c>
       <c r="BQ44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR44" t="n">
         <v>1000</v>
       </c>
       <c r="BS44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT44" t="n">
         <v>1000</v>
       </c>
       <c r="BU44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV44" t="n">
         <v>1000</v>
       </c>
       <c r="BW44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX44" t="n">
         <v>1000</v>
       </c>
       <c r="BY44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ44" t="n">
         <v>1000</v>
       </c>
       <c r="CA44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -11797,7 +11797,7 @@
         <v>4.5</v>
       </c>
       <c r="L45" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M45" t="n">
         <v>1.08</v>
@@ -11944,7 +11944,7 @@
         <v>3.2</v>
       </c>
       <c r="BI45" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="BJ45" t="n">
         <v>13</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
         <v>1.86</v>
       </c>
       <c r="G46" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H46" t="n">
         <v>5.1</v>
@@ -12045,10 +12045,10 @@
         <v>5.8</v>
       </c>
       <c r="J46" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -12084,7 +12084,7 @@
         <v>1.2</v>
       </c>
       <c r="W46" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
         <v>3.4</v>
       </c>
       <c r="I47" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J47" t="n">
         <v>3</v>
@@ -12335,10 +12335,10 @@
         <v>1.85</v>
       </c>
       <c r="V47" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W47" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X47" t="n">
         <v>12.5</v>
@@ -12362,7 +12362,7 @@
         <v>19.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF47" t="n">
         <v>17</v>
@@ -12398,7 +12398,7 @@
         <v>7.6</v>
       </c>
       <c r="AQ47" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR47" t="n">
         <v>18</v>
@@ -12431,7 +12431,7 @@
         <v>4.1</v>
       </c>
       <c r="BB47" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BC47" t="n">
         <v>21</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -12706,65 +12706,65 @@
         <v>1000</v>
       </c>
       <c r="BI48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ48" t="n">
         <v>1000</v>
       </c>
       <c r="BK48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN48" t="n">
         <v>1000</v>
       </c>
       <c r="BO48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP48" t="n">
         <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR48" t="n">
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT48" t="n">
         <v>1000</v>
       </c>
       <c r="BU48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV48" t="n">
         <v>1000</v>
       </c>
       <c r="BW48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX48" t="n">
         <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ48" t="n">
         <v>1000</v>
       </c>
       <c r="CA48" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -12828,7 +12828,7 @@
         <v>1.76</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="R49" t="n">
         <v>1.25</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -13214,65 +13214,65 @@
         <v>1000</v>
       </c>
       <c r="BI50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ50" t="n">
         <v>1000</v>
       </c>
       <c r="BK50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL50" t="n">
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN50" t="n">
         <v>1000</v>
       </c>
       <c r="BO50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP50" t="n">
         <v>1000</v>
       </c>
       <c r="BQ50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR50" t="n">
         <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT50" t="n">
         <v>1000</v>
       </c>
       <c r="BU50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV50" t="n">
         <v>1000</v>
       </c>
       <c r="BW50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX50" t="n">
         <v>1000</v>
       </c>
       <c r="BY50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ50" t="n">
         <v>1000</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -13468,65 +13468,65 @@
         <v>1000</v>
       </c>
       <c r="BI51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ51" t="n">
         <v>1000</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN51" t="n">
         <v>1000</v>
       </c>
       <c r="BO51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP51" t="n">
         <v>1000</v>
       </c>
       <c r="BQ51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR51" t="n">
         <v>1000</v>
       </c>
       <c r="BS51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT51" t="n">
         <v>1000</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV51" t="n">
         <v>1000</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX51" t="n">
         <v>1000</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ51" t="n">
         <v>1000</v>
       </c>
       <c r="CA51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -13722,65 +13722,65 @@
         <v>1000</v>
       </c>
       <c r="BI52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ52" t="n">
         <v>1000</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN52" t="n">
         <v>1000</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP52" t="n">
         <v>1000</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR52" t="n">
         <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT52" t="n">
         <v>1000</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV52" t="n">
         <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX52" t="n">
         <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ52" t="n">
         <v>1000</v>
       </c>
       <c r="CA52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -13976,65 +13976,65 @@
         <v>1000</v>
       </c>
       <c r="BI53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ53" t="n">
         <v>1000</v>
       </c>
       <c r="BK53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL53" t="n">
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN53" t="n">
         <v>1000</v>
       </c>
       <c r="BO53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP53" t="n">
         <v>1000</v>
       </c>
       <c r="BQ53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR53" t="n">
         <v>1000</v>
       </c>
       <c r="BS53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT53" t="n">
         <v>1000</v>
       </c>
       <c r="BU53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV53" t="n">
         <v>1000</v>
       </c>
       <c r="BW53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX53" t="n">
         <v>1000</v>
       </c>
       <c r="BY53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ53" t="n">
         <v>1000</v>
       </c>
       <c r="CA53" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -14230,65 +14230,65 @@
         <v>1000</v>
       </c>
       <c r="BI54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ54" t="n">
         <v>1000</v>
       </c>
       <c r="BK54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL54" t="n">
         <v>1000</v>
       </c>
       <c r="BM54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN54" t="n">
         <v>1000</v>
       </c>
       <c r="BO54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP54" t="n">
         <v>1000</v>
       </c>
       <c r="BQ54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR54" t="n">
         <v>1000</v>
       </c>
       <c r="BS54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT54" t="n">
         <v>1000</v>
       </c>
       <c r="BU54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV54" t="n">
         <v>1000</v>
       </c>
       <c r="BW54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX54" t="n">
         <v>1000</v>
       </c>
       <c r="BY54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ54" t="n">
         <v>1000</v>
       </c>
       <c r="CA54" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -14325,7 +14325,7 @@
         <v>2.76</v>
       </c>
       <c r="H55" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I55" t="n">
         <v>2.62</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
         <v>19</v>
       </c>
       <c r="Z56" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA56" t="n">
         <v>75</v>
@@ -14660,7 +14660,7 @@
         <v>19</v>
       </c>
       <c r="AI56" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ56" t="n">
         <v>30</v>
@@ -14738,65 +14738,65 @@
         <v>1000</v>
       </c>
       <c r="BI56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ56" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN56" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO56" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP56" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR56" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT56" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU56" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV56" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX56" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ56" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -14857,16 +14857,16 @@
         <v>1.25</v>
       </c>
       <c r="P57" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="R57" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S57" t="n">
-        <v>2.84</v>
+        <v>2.52</v>
       </c>
       <c r="T57" t="n">
         <v>1.63</v>
@@ -14932,7 +14932,7 @@
         <v>25</v>
       </c>
       <c r="AO57" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP57" t="n">
         <v>13.5</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -15081,10 +15081,10 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G58" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H58" t="n">
         <v>4</v>
@@ -15105,34 +15105,34 @@
         <v>1.08</v>
       </c>
       <c r="N58" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O58" t="n">
         <v>1.37</v>
       </c>
       <c r="P58" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R58" t="n">
         <v>1.31</v>
       </c>
       <c r="S58" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T58" t="n">
         <v>1.89</v>
       </c>
       <c r="U58" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V58" t="n">
         <v>1.31</v>
       </c>
       <c r="W58" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X58" t="n">
         <v>15.5</v>
@@ -15141,7 +15141,7 @@
         <v>17</v>
       </c>
       <c r="Z58" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA58" t="n">
         <v>120</v>
@@ -15156,7 +15156,7 @@
         <v>21</v>
       </c>
       <c r="AE58" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF58" t="n">
         <v>15</v>
@@ -15186,7 +15186,7 @@
         <v>22</v>
       </c>
       <c r="AO58" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP58" t="n">
         <v>9.4</v>
@@ -15195,10 +15195,10 @@
         <v>10</v>
       </c>
       <c r="AR58" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS58" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT58" t="n">
         <v>7.6</v>
@@ -15210,7 +15210,7 @@
         <v>12.5</v>
       </c>
       <c r="AW58" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX58" t="n">
         <v>9.199999999999999</v>
@@ -15222,28 +15222,28 @@
         <v>14</v>
       </c>
       <c r="BA58" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB58" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC58" t="n">
         <v>17</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE58" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF58" t="n">
         <v>12.5</v>
       </c>
       <c r="BG58" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH58" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI58" t="n">
         <v>2.66</v>
@@ -15252,13 +15252,13 @@
         <v>10.5</v>
       </c>
       <c r="BK58" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL58" t="n">
         <v>1000</v>
       </c>
       <c r="BM58" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN58" t="n">
         <v>4.7</v>
@@ -15270,13 +15270,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ58" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR58" t="n">
         <v>1000</v>
       </c>
       <c r="BS58" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT58" t="n">
         <v>7.4</v>
@@ -15288,23 +15288,23 @@
         <v>1000</v>
       </c>
       <c r="BW58" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX58" t="n">
         <v>1000</v>
       </c>
       <c r="BY58" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ58" t="n">
         <v>1000</v>
       </c>
       <c r="CA58" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -15338,13 +15338,13 @@
         <v>1.96</v>
       </c>
       <c r="G59" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="H59" t="n">
         <v>3.35</v>
       </c>
       <c r="I59" t="n">
-        <v>990</v>
+        <v>5.6</v>
       </c>
       <c r="J59" t="n">
         <v>2.96</v>
@@ -15383,7 +15383,7 @@
         <v>1.11</v>
       </c>
       <c r="V59" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W59" t="n">
         <v>1.62</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -15607,10 +15607,10 @@
         <v>4.4</v>
       </c>
       <c r="L60" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M60" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N60" t="n">
         <v>3.5</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -15876,7 +15876,7 @@
         <v>1.25</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="R61" t="n">
         <v>1.24</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -16097,16 +16097,16 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G62" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H62" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I62" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J62" t="n">
         <v>4.2</v>
@@ -16121,34 +16121,34 @@
         <v>1.06</v>
       </c>
       <c r="N62" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O62" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P62" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R62" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S62" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T62" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="U62" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V62" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W62" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X62" t="n">
         <v>19.5</v>
@@ -16217,10 +16217,10 @@
         <v>5.1</v>
       </c>
       <c r="AT62" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU62" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV62" t="n">
         <v>19</v>
@@ -16229,7 +16229,7 @@
         <v>5</v>
       </c>
       <c r="AX62" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY62" t="n">
         <v>7.8</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -16516,65 +16516,65 @@
         <v>1000</v>
       </c>
       <c r="BI63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ63" t="n">
         <v>1000</v>
       </c>
       <c r="BK63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL63" t="n">
         <v>1000</v>
       </c>
       <c r="BM63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN63" t="n">
         <v>1000</v>
       </c>
       <c r="BO63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP63" t="n">
         <v>1000</v>
       </c>
       <c r="BQ63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR63" t="n">
         <v>1000</v>
       </c>
       <c r="BS63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT63" t="n">
         <v>1000</v>
       </c>
       <c r="BU63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV63" t="n">
         <v>1000</v>
       </c>
       <c r="BW63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX63" t="n">
         <v>1000</v>
       </c>
       <c r="BY63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ63" t="n">
         <v>1000</v>
       </c>
       <c r="CA63" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -16611,10 +16611,10 @@
         <v>4.4</v>
       </c>
       <c r="H64" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J64" t="n">
         <v>3.7</v>
@@ -16635,7 +16635,7 @@
         <v>1.41</v>
       </c>
       <c r="P64" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q64" t="n">
         <v>2.26</v>
@@ -16722,7 +16722,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT64" t="n">
         <v>12.5</v>
@@ -16743,7 +16743,7 @@
         <v>16</v>
       </c>
       <c r="AZ64" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA64" t="n">
         <v>40</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -17131,7 +17131,7 @@
         <v>3.75</v>
       </c>
       <c r="L66" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M66" t="n">
         <v>1.08</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -17645,10 +17645,10 @@
         <v>1.01</v>
       </c>
       <c r="N68" t="n">
-        <v>2.72</v>
+        <v>4.6</v>
       </c>
       <c r="O68" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="P68" t="n">
         <v>2.24</v>
@@ -17657,7 +17657,7 @@
         <v>1.65</v>
       </c>
       <c r="R68" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S68" t="n">
         <v>2.56</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -17887,7 +17887,7 @@
         <v>12.5</v>
       </c>
       <c r="J69" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K69" t="n">
         <v>5.9</v>
@@ -17908,7 +17908,7 @@
         <v>2.2</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="R69" t="n">
         <v>1.4</v>
@@ -18040,65 +18040,65 @@
         <v>1000</v>
       </c>
       <c r="BI69" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BJ69" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK69" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BL69" t="n">
         <v>1000</v>
       </c>
       <c r="BM69" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BN69" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO69" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BP69" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ69" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR69" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS69" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BT69" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BU69" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BV69" t="n">
         <v>1000</v>
       </c>
       <c r="BW69" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BX69" t="n">
         <v>1000</v>
       </c>
       <c r="BY69" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BZ69" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA69" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -18174,7 +18174,7 @@
         <v>1.11</v>
       </c>
       <c r="U70" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V70" t="n">
         <v>2.28</v>
@@ -18294,65 +18294,65 @@
         <v>1000</v>
       </c>
       <c r="BI70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ70" t="n">
         <v>1000</v>
       </c>
       <c r="BK70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL70" t="n">
         <v>1000</v>
       </c>
       <c r="BM70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN70" t="n">
         <v>1000</v>
       </c>
       <c r="BO70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP70" t="n">
         <v>1000</v>
       </c>
       <c r="BQ70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR70" t="n">
         <v>1000</v>
       </c>
       <c r="BS70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT70" t="n">
         <v>1000</v>
       </c>
       <c r="BU70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV70" t="n">
         <v>1000</v>
       </c>
       <c r="BW70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX70" t="n">
         <v>1000</v>
       </c>
       <c r="BY70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ70" t="n">
         <v>1000</v>
       </c>
       <c r="CA70" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -18419,7 +18419,7 @@
         <v>2.1</v>
       </c>
       <c r="R71" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S71" t="n">
         <v>3.5</v>
@@ -18548,65 +18548,65 @@
         <v>1000</v>
       </c>
       <c r="BI71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ71" t="n">
         <v>1000</v>
       </c>
       <c r="BK71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL71" t="n">
         <v>1000</v>
       </c>
       <c r="BM71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN71" t="n">
         <v>1000</v>
       </c>
       <c r="BO71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP71" t="n">
         <v>1000</v>
       </c>
       <c r="BQ71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR71" t="n">
         <v>1000</v>
       </c>
       <c r="BS71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT71" t="n">
         <v>1000</v>
       </c>
       <c r="BU71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV71" t="n">
         <v>1000</v>
       </c>
       <c r="BW71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX71" t="n">
         <v>1000</v>
       </c>
       <c r="BY71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ71" t="n">
         <v>1000</v>
       </c>
       <c r="CA71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -18802,65 +18802,65 @@
         <v>1000</v>
       </c>
       <c r="BI72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ72" t="n">
         <v>1000</v>
       </c>
       <c r="BK72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL72" t="n">
         <v>1000</v>
       </c>
       <c r="BM72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN72" t="n">
         <v>1000</v>
       </c>
       <c r="BO72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP72" t="n">
         <v>1000</v>
       </c>
       <c r="BQ72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR72" t="n">
         <v>1000</v>
       </c>
       <c r="BS72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT72" t="n">
         <v>1000</v>
       </c>
       <c r="BU72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV72" t="n">
         <v>1000</v>
       </c>
       <c r="BW72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX72" t="n">
         <v>1000</v>
       </c>
       <c r="BY72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ72" t="n">
         <v>1000</v>
       </c>
       <c r="CA72" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -18891,7 +18891,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="G73" t="n">
         <v>1.39</v>
@@ -18939,7 +18939,7 @@
         <v>1.11</v>
       </c>
       <c r="V73" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W73" t="n">
         <v>3.45</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -19145,46 +19145,46 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="G74" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H74" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="I74" t="n">
         <v>7.8</v>
       </c>
       <c r="J74" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="K74" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="L74" t="n">
         <v>1.01</v>
       </c>
       <c r="M74" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N74" t="n">
-        <v>4.2</v>
+        <v>2.06</v>
       </c>
       <c r="O74" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="P74" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R74" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S74" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T74" t="n">
         <v>1.63</v>
@@ -19193,10 +19193,10 @@
         <v>1.94</v>
       </c>
       <c r="V74" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W74" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="X74" t="n">
         <v>27</v>
@@ -19310,65 +19310,65 @@
         <v>1000</v>
       </c>
       <c r="BI74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ74" t="n">
         <v>1000</v>
       </c>
       <c r="BK74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL74" t="n">
         <v>1000</v>
       </c>
       <c r="BM74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN74" t="n">
         <v>1000</v>
       </c>
       <c r="BO74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP74" t="n">
         <v>1000</v>
       </c>
       <c r="BQ74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR74" t="n">
         <v>1000</v>
       </c>
       <c r="BS74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT74" t="n">
         <v>1000</v>
       </c>
       <c r="BU74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV74" t="n">
         <v>1000</v>
       </c>
       <c r="BW74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX74" t="n">
         <v>1000</v>
       </c>
       <c r="BY74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ74" t="n">
         <v>1000</v>
       </c>
       <c r="CA74" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -19564,65 +19564,65 @@
         <v>1000</v>
       </c>
       <c r="BI75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ75" t="n">
         <v>1000</v>
       </c>
       <c r="BK75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL75" t="n">
         <v>1000</v>
       </c>
       <c r="BM75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN75" t="n">
         <v>1000</v>
       </c>
       <c r="BO75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP75" t="n">
         <v>1000</v>
       </c>
       <c r="BQ75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR75" t="n">
         <v>1000</v>
       </c>
       <c r="BS75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT75" t="n">
         <v>1000</v>
       </c>
       <c r="BU75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV75" t="n">
         <v>1000</v>
       </c>
       <c r="BW75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX75" t="n">
         <v>1000</v>
       </c>
       <c r="BY75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ75" t="n">
         <v>1000</v>
       </c>
       <c r="CA75" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -19653,22 +19653,22 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="G76" t="n">
         <v>1.47</v>
       </c>
       <c r="H76" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="I76" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J76" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K76" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="L76" t="n">
         <v>1.01</v>
@@ -19818,65 +19818,65 @@
         <v>1000</v>
       </c>
       <c r="BI76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ76" t="n">
         <v>1000</v>
       </c>
       <c r="BK76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL76" t="n">
         <v>1000</v>
       </c>
       <c r="BM76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN76" t="n">
         <v>1000</v>
       </c>
       <c r="BO76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP76" t="n">
         <v>1000</v>
       </c>
       <c r="BQ76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR76" t="n">
         <v>1000</v>
       </c>
       <c r="BS76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT76" t="n">
         <v>1000</v>
       </c>
       <c r="BU76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV76" t="n">
         <v>1000</v>
       </c>
       <c r="BW76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX76" t="n">
         <v>1000</v>
       </c>
       <c r="BY76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ76" t="n">
         <v>1000</v>
       </c>
       <c r="CA76" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -19907,10 +19907,10 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G77" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="H77" t="n">
         <v>4.9</v>
@@ -19949,16 +19949,16 @@
         <v>2.08</v>
       </c>
       <c r="T77" t="n">
-        <v>1.46</v>
+        <v>1.11</v>
       </c>
       <c r="U77" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="V77" t="n">
         <v>1.12</v>
       </c>
       <c r="W77" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="X77" t="n">
         <v>1000</v>
@@ -20072,65 +20072,65 @@
         <v>1000</v>
       </c>
       <c r="BI77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ77" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL77" t="n">
         <v>1000</v>
       </c>
       <c r="BM77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN77" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP77" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR77" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT77" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV77" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX77" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ77" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="CA77" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -20326,65 +20326,65 @@
         <v>1000</v>
       </c>
       <c r="BI78" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ78" t="n">
         <v>1000</v>
       </c>
       <c r="BK78" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL78" t="n">
         <v>1000</v>
       </c>
       <c r="BM78" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN78" t="n">
         <v>1000</v>
       </c>
       <c r="BO78" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP78" t="n">
         <v>1000</v>
       </c>
       <c r="BQ78" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR78" t="n">
         <v>1000</v>
       </c>
       <c r="BS78" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT78" t="n">
         <v>1000</v>
       </c>
       <c r="BU78" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV78" t="n">
         <v>1000</v>
       </c>
       <c r="BW78" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX78" t="n">
         <v>1000</v>
       </c>
       <c r="BY78" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ78" t="n">
         <v>1000</v>
       </c>
       <c r="CA78" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -20418,10 +20418,10 @@
         <v>3.2</v>
       </c>
       <c r="G79" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H79" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I79" t="n">
         <v>2.34</v>
@@ -20532,7 +20532,7 @@
         <v>16</v>
       </c>
       <c r="AS79" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AT79" t="n">
         <v>17</v>
@@ -20547,7 +20547,7 @@
         <v>19</v>
       </c>
       <c r="AX79" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY79" t="n">
         <v>13</v>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -20690,10 +20690,10 @@
         <v>1.01</v>
       </c>
       <c r="M80" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N80" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="O80" t="n">
         <v>1.26</v>
@@ -20840,59 +20840,59 @@
         <v>1000</v>
       </c>
       <c r="BK80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL80" t="n">
         <v>1000</v>
       </c>
       <c r="BM80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN80" t="n">
         <v>1000</v>
       </c>
       <c r="BO80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP80" t="n">
         <v>1000</v>
       </c>
       <c r="BQ80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR80" t="n">
         <v>1000</v>
       </c>
       <c r="BS80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT80" t="n">
         <v>1000</v>
       </c>
       <c r="BU80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV80" t="n">
         <v>1000</v>
       </c>
       <c r="BW80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX80" t="n">
         <v>1000</v>
       </c>
       <c r="BY80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ80" t="n">
         <v>1000</v>
       </c>
       <c r="CA80" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB80" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -21146,7 +21146,7 @@
       </c>
       <c r="CB81" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -21177,7 +21177,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G82" t="n">
         <v>3.15</v>
@@ -21189,10 +21189,10 @@
         <v>3.4</v>
       </c>
       <c r="J82" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="K82" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L82" t="n">
         <v>1.01</v>
@@ -21201,7 +21201,7 @@
         <v>1.01</v>
       </c>
       <c r="N82" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O82" t="n">
         <v>1.02</v>
@@ -21210,7 +21210,7 @@
         <v>1.44</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R82" t="n">
         <v>1.18</v>
@@ -21228,7 +21228,7 @@
         <v>1.42</v>
       </c>
       <c r="W82" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="X82" t="n">
         <v>10.5</v>
@@ -21237,10 +21237,10 @@
         <v>11</v>
       </c>
       <c r="Z82" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA82" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB82" t="n">
         <v>9.800000000000001</v>
@@ -21297,7 +21297,7 @@
         <v>1.01</v>
       </c>
       <c r="AT82" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU82" t="n">
         <v>5.3</v>
@@ -21312,7 +21312,7 @@
         <v>12</v>
       </c>
       <c r="AY82" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ82" t="n">
         <v>1.03</v>
@@ -21342,65 +21342,65 @@
         <v>1000</v>
       </c>
       <c r="BI82" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ82" t="n">
         <v>1000</v>
       </c>
       <c r="BK82" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL82" t="n">
         <v>1000</v>
       </c>
       <c r="BM82" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN82" t="n">
         <v>1000</v>
       </c>
       <c r="BO82" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP82" t="n">
         <v>1000</v>
       </c>
       <c r="BQ82" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR82" t="n">
         <v>1000</v>
       </c>
       <c r="BS82" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT82" t="n">
         <v>1000</v>
       </c>
       <c r="BU82" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV82" t="n">
         <v>1000</v>
       </c>
       <c r="BW82" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX82" t="n">
         <v>1000</v>
       </c>
       <c r="BY82" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ82" t="n">
         <v>1000</v>
       </c>
       <c r="CA82" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB82" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -21654,7 +21654,7 @@
       </c>
       <c r="CB83" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -21724,7 +21724,7 @@
         <v>1.22</v>
       </c>
       <c r="S84" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T84" t="n">
         <v>2.04</v>
@@ -21908,7 +21908,7 @@
       </c>
       <c r="CB84" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -21978,7 +21978,7 @@
         <v>1.12</v>
       </c>
       <c r="S85" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="T85" t="n">
         <v>2.34</v>
@@ -22104,65 +22104,65 @@
         <v>1000</v>
       </c>
       <c r="BI85" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ85" t="n">
         <v>1000</v>
       </c>
       <c r="BK85" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL85" t="n">
         <v>1000</v>
       </c>
       <c r="BM85" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN85" t="n">
         <v>1000</v>
       </c>
       <c r="BO85" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP85" t="n">
         <v>1000</v>
       </c>
       <c r="BQ85" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR85" t="n">
         <v>1000</v>
       </c>
       <c r="BS85" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT85" t="n">
         <v>1000</v>
       </c>
       <c r="BU85" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV85" t="n">
         <v>1000</v>
       </c>
       <c r="BW85" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX85" t="n">
         <v>1000</v>
       </c>
       <c r="BY85" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ85" t="n">
         <v>1000</v>
       </c>
       <c r="CA85" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB85" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -22193,7 +22193,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="G86" t="n">
         <v>2.08</v>
@@ -22202,13 +22202,13 @@
         <v>4.1</v>
       </c>
       <c r="I86" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J86" t="n">
         <v>3.45</v>
       </c>
       <c r="K86" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L86" t="n">
         <v>1.01</v>
@@ -22416,7 +22416,7 @@
       </c>
       <c r="CB86" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -22612,65 +22612,65 @@
         <v>1000</v>
       </c>
       <c r="BI87" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ87" t="n">
         <v>1000</v>
       </c>
       <c r="BK87" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL87" t="n">
         <v>1000</v>
       </c>
       <c r="BM87" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN87" t="n">
         <v>1000</v>
       </c>
       <c r="BO87" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP87" t="n">
         <v>1000</v>
       </c>
       <c r="BQ87" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR87" t="n">
         <v>1000</v>
       </c>
       <c r="BS87" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT87" t="n">
         <v>1000</v>
       </c>
       <c r="BU87" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV87" t="n">
         <v>1000</v>
       </c>
       <c r="BW87" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX87" t="n">
         <v>1000</v>
       </c>
       <c r="BY87" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ87" t="n">
         <v>1000</v>
       </c>
       <c r="CA87" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB87" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -22725,7 +22725,7 @@
         <v>1.01</v>
       </c>
       <c r="N88" t="n">
-        <v>2.78</v>
+        <v>2.24</v>
       </c>
       <c r="O88" t="n">
         <v>1.2</v>
@@ -22737,7 +22737,7 @@
         <v>1.66</v>
       </c>
       <c r="R88" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S88" t="n">
         <v>2.52</v>
@@ -22924,7 +22924,7 @@
       </c>
       <c r="CB88" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -23178,7 +23178,7 @@
       </c>
       <c r="CB89" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -23212,13 +23212,13 @@
         <v>2.34</v>
       </c>
       <c r="G90" t="n">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="H90" t="n">
         <v>3.15</v>
       </c>
       <c r="I90" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="J90" t="n">
         <v>3.1</v>
@@ -23257,10 +23257,10 @@
         <v>1.69</v>
       </c>
       <c r="V90" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W90" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="X90" t="n">
         <v>15.5</v>
@@ -23432,7 +23432,7 @@
       </c>
       <c r="CB90" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -23481,13 +23481,13 @@
         <v>4.6</v>
       </c>
       <c r="L91" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M91" t="n">
         <v>1.01</v>
       </c>
       <c r="N91" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O91" t="n">
         <v>1.24</v>
@@ -23496,10 +23496,10 @@
         <v>2.02</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R91" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S91" t="n">
         <v>2.84</v>
@@ -23628,65 +23628,65 @@
         <v>1000</v>
       </c>
       <c r="BI91" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ91" t="n">
         <v>1000</v>
       </c>
       <c r="BK91" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL91" t="n">
         <v>1000</v>
       </c>
       <c r="BM91" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN91" t="n">
         <v>1000</v>
       </c>
       <c r="BO91" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP91" t="n">
         <v>1000</v>
       </c>
       <c r="BQ91" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR91" t="n">
         <v>1000</v>
       </c>
       <c r="BS91" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT91" t="n">
         <v>1000</v>
       </c>
       <c r="BU91" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV91" t="n">
         <v>1000</v>
       </c>
       <c r="BW91" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX91" t="n">
         <v>1000</v>
       </c>
       <c r="BY91" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ91" t="n">
         <v>1000</v>
       </c>
       <c r="CA91" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB91" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -23723,7 +23723,7 @@
         <v>1.62</v>
       </c>
       <c r="H92" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I92" t="n">
         <v>6.8</v>
@@ -23831,7 +23831,7 @@
         <v>19.5</v>
       </c>
       <c r="AR92" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AS92" t="n">
         <v>46</v>
@@ -23882,7 +23882,7 @@
         <v>3.7</v>
       </c>
       <c r="BI92" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BJ92" t="n">
         <v>10.5</v>
@@ -23940,7 +23940,7 @@
       </c>
       <c r="CB92" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -23971,13 +23971,13 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G93" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H93" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="I93" t="n">
         <v>2.02</v>
@@ -24019,10 +24019,10 @@
         <v>2.42</v>
       </c>
       <c r="V93" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="W93" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X93" t="n">
         <v>29</v>
@@ -24034,7 +24034,7 @@
         <v>17.5</v>
       </c>
       <c r="AA93" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB93" t="n">
         <v>24</v>
@@ -24103,7 +24103,7 @@
         <v>15.5</v>
       </c>
       <c r="AX93" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY93" t="n">
         <v>14</v>
@@ -24112,13 +24112,13 @@
         <v>13.5</v>
       </c>
       <c r="BA93" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB93" t="n">
         <v>4.6</v>
       </c>
       <c r="BC93" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD93" t="n">
         <v>4.5</v>
@@ -24136,19 +24136,19 @@
         <v>1000</v>
       </c>
       <c r="BI93" t="n">
-        <v>2.96</v>
+        <v>1.97</v>
       </c>
       <c r="BJ93" t="n">
         <v>12.5</v>
       </c>
       <c r="BK93" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="BL93" t="n">
         <v>1000</v>
       </c>
       <c r="BM93" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="BN93" t="n">
         <v>10.5</v>
@@ -24157,7 +24157,7 @@
         <v>4.9</v>
       </c>
       <c r="BP93" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ93" t="n">
         <v>1.89</v>
@@ -24166,7 +24166,7 @@
         <v>48</v>
       </c>
       <c r="BS93" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="BT93" t="n">
         <v>7</v>
@@ -24178,23 +24178,23 @@
         <v>18</v>
       </c>
       <c r="BW93" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="BX93" t="n">
         <v>32</v>
       </c>
       <c r="BY93" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="BZ93" t="n">
         <v>23</v>
       </c>
       <c r="CA93" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="CB93" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -24448,7 +24448,7 @@
       </c>
       <c r="CB94" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -24527,7 +24527,7 @@
         <v>1.98</v>
       </c>
       <c r="V95" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W95" t="n">
         <v>1.74</v>
@@ -24644,65 +24644,65 @@
         <v>1000</v>
       </c>
       <c r="BI95" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ95" t="n">
         <v>1000</v>
       </c>
       <c r="BK95" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL95" t="n">
         <v>1000</v>
       </c>
       <c r="BM95" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN95" t="n">
         <v>1000</v>
       </c>
       <c r="BO95" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP95" t="n">
         <v>1000</v>
       </c>
       <c r="BQ95" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR95" t="n">
         <v>1000</v>
       </c>
       <c r="BS95" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT95" t="n">
         <v>1000</v>
       </c>
       <c r="BU95" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV95" t="n">
         <v>1000</v>
       </c>
       <c r="BW95" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX95" t="n">
         <v>1000</v>
       </c>
       <c r="BY95" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ95" t="n">
         <v>1000</v>
       </c>
       <c r="CA95" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB95" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -24763,7 +24763,7 @@
         <v>1.16</v>
       </c>
       <c r="P96" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q96" t="n">
         <v>1.16</v>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="CB96" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -25152,65 +25152,65 @@
         <v>1000</v>
       </c>
       <c r="BI97" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ97" t="n">
         <v>1000</v>
       </c>
       <c r="BK97" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL97" t="n">
         <v>1000</v>
       </c>
       <c r="BM97" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN97" t="n">
         <v>1000</v>
       </c>
       <c r="BO97" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP97" t="n">
         <v>1000</v>
       </c>
       <c r="BQ97" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR97" t="n">
         <v>1000</v>
       </c>
       <c r="BS97" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT97" t="n">
         <v>1000</v>
       </c>
       <c r="BU97" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV97" t="n">
         <v>1000</v>
       </c>
       <c r="BW97" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX97" t="n">
         <v>1000</v>
       </c>
       <c r="BY97" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ97" t="n">
         <v>1000</v>
       </c>
       <c r="CA97" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB97" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -25464,7 +25464,7 @@
       </c>
       <c r="CB98" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -25660,65 +25660,65 @@
         <v>1000</v>
       </c>
       <c r="BI99" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ99" t="n">
         <v>1000</v>
       </c>
       <c r="BK99" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL99" t="n">
         <v>1000</v>
       </c>
       <c r="BM99" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN99" t="n">
         <v>1000</v>
       </c>
       <c r="BO99" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP99" t="n">
         <v>1000</v>
       </c>
       <c r="BQ99" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR99" t="n">
         <v>1000</v>
       </c>
       <c r="BS99" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT99" t="n">
         <v>1000</v>
       </c>
       <c r="BU99" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV99" t="n">
         <v>1000</v>
       </c>
       <c r="BW99" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX99" t="n">
         <v>1000</v>
       </c>
       <c r="BY99" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ99" t="n">
         <v>1000</v>
       </c>
       <c r="CA99" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB99" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -25972,7 +25972,7 @@
       </c>
       <c r="CB100" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -26141,7 +26141,7 @@
         <v>14</v>
       </c>
       <c r="AZ101" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA101" t="n">
         <v>36</v>
@@ -26168,65 +26168,65 @@
         <v>1000</v>
       </c>
       <c r="BI101" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ101" t="n">
         <v>1000</v>
       </c>
       <c r="BK101" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL101" t="n">
         <v>1000</v>
       </c>
       <c r="BM101" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN101" t="n">
         <v>1000</v>
       </c>
       <c r="BO101" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP101" t="n">
         <v>1000</v>
       </c>
       <c r="BQ101" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR101" t="n">
         <v>1000</v>
       </c>
       <c r="BS101" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT101" t="n">
         <v>1000</v>
       </c>
       <c r="BU101" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV101" t="n">
         <v>1000</v>
       </c>
       <c r="BW101" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX101" t="n">
         <v>1000</v>
       </c>
       <c r="BY101" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ101" t="n">
         <v>1000</v>
       </c>
       <c r="CA101" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB101" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -26263,10 +26263,10 @@
         <v>1.53</v>
       </c>
       <c r="H102" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I102" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J102" t="n">
         <v>4.7</v>
@@ -26422,7 +26422,7 @@
         <v>1000</v>
       </c>
       <c r="BI102" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BJ102" t="n">
         <v>17.5</v>
@@ -26434,7 +26434,7 @@
         <v>1000</v>
       </c>
       <c r="BM102" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BN102" t="n">
         <v>5.3</v>
@@ -26464,13 +26464,13 @@
         <v>1000</v>
       </c>
       <c r="BW102" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BX102" t="n">
         <v>1000</v>
       </c>
       <c r="BY102" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BZ102" t="n">
         <v>25</v>
@@ -26480,7 +26480,7 @@
       </c>
       <c r="CB102" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -26676,7 +26676,7 @@
         <v>3</v>
       </c>
       <c r="BI103" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ103" t="n">
         <v>1000</v>
@@ -26734,7 +26734,7 @@
       </c>
       <c r="CB103" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -26988,7 +26988,7 @@
       </c>
       <c r="CB104" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -27175,10 +27175,10 @@
         <v>42</v>
       </c>
       <c r="BF105" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG105" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BH105" t="n">
         <v>1000</v>
@@ -27242,7 +27242,7 @@
       </c>
       <c r="CB105" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="CB106" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -27533,7 +27533,7 @@
         <v>3.9</v>
       </c>
       <c r="H107" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="I107" t="n">
         <v>1.95</v>
@@ -27750,7 +27750,7 @@
       </c>
       <c r="CB107" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -27790,7 +27790,7 @@
         <v>4.6</v>
       </c>
       <c r="I108" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J108" t="n">
         <v>4.1</v>
@@ -27829,7 +27829,7 @@
         <v>2.3</v>
       </c>
       <c r="V108" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W108" t="n">
         <v>2.18</v>
@@ -27841,7 +27841,7 @@
         <v>19</v>
       </c>
       <c r="Z108" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA108" t="n">
         <v>110</v>
@@ -27853,7 +27853,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD108" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE108" t="n">
         <v>55</v>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="CB108" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -28173,7 +28173,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ109" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA109" t="n">
         <v>55</v>
@@ -28191,7 +28191,7 @@
         <v>65</v>
       </c>
       <c r="BF109" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BG109" t="n">
         <v>55</v>
@@ -28258,7 +28258,7 @@
       </c>
       <c r="CB109" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -28512,7 +28512,7 @@
       </c>
       <c r="CB110" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -28543,22 +28543,22 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="G111" t="n">
         <v>2.42</v>
       </c>
       <c r="H111" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="I111" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J111" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="K111" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L111" t="n">
         <v>1.01</v>
@@ -28573,7 +28573,7 @@
         <v>1.33</v>
       </c>
       <c r="P111" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="Q111" t="n">
         <v>2</v>
@@ -28708,65 +28708,65 @@
         <v>1000</v>
       </c>
       <c r="BI111" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ111" t="n">
         <v>1000</v>
       </c>
       <c r="BK111" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL111" t="n">
         <v>1000</v>
       </c>
       <c r="BM111" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN111" t="n">
         <v>1000</v>
       </c>
       <c r="BO111" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP111" t="n">
         <v>1000</v>
       </c>
       <c r="BQ111" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR111" t="n">
         <v>1000</v>
       </c>
       <c r="BS111" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT111" t="n">
         <v>1000</v>
       </c>
       <c r="BU111" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV111" t="n">
         <v>1000</v>
       </c>
       <c r="BW111" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX111" t="n">
         <v>1000</v>
       </c>
       <c r="BY111" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ111" t="n">
         <v>1000</v>
       </c>
       <c r="CA111" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB111" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -28839,7 +28839,7 @@
         <v>3.35</v>
       </c>
       <c r="T112" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U112" t="n">
         <v>2.16</v>
@@ -29020,7 +29020,7 @@
       </c>
       <c r="CB112" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -29099,7 +29099,7 @@
         <v>1.92</v>
       </c>
       <c r="V113" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W113" t="n">
         <v>1.43</v>
@@ -29274,7 +29274,7 @@
       </c>
       <c r="CB113" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -29470,65 +29470,65 @@
         <v>1000</v>
       </c>
       <c r="BI114" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ114" t="n">
         <v>1000</v>
       </c>
       <c r="BK114" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL114" t="n">
         <v>1000</v>
       </c>
       <c r="BM114" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN114" t="n">
         <v>1000</v>
       </c>
       <c r="BO114" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP114" t="n">
         <v>1000</v>
       </c>
       <c r="BQ114" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR114" t="n">
         <v>1000</v>
       </c>
       <c r="BS114" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT114" t="n">
         <v>1000</v>
       </c>
       <c r="BU114" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV114" t="n">
         <v>1000</v>
       </c>
       <c r="BW114" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX114" t="n">
         <v>1000</v>
       </c>
       <c r="BY114" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ114" t="n">
         <v>1000</v>
       </c>
       <c r="CA114" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB114" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -29782,7 +29782,7 @@
       </c>
       <c r="CB115" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -29813,7 +29813,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G116" t="n">
         <v>3.75</v>
@@ -29978,65 +29978,65 @@
         <v>1000</v>
       </c>
       <c r="BI116" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ116" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK116" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL116" t="n">
         <v>1000</v>
       </c>
       <c r="BM116" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN116" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO116" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP116" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ116" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR116" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS116" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT116" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU116" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV116" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW116" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX116" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY116" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ116" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA116" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB116" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -30232,65 +30232,65 @@
         <v>1000</v>
       </c>
       <c r="BI117" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ117" t="n">
         <v>1000</v>
       </c>
       <c r="BK117" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL117" t="n">
         <v>1000</v>
       </c>
       <c r="BM117" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN117" t="n">
         <v>1000</v>
       </c>
       <c r="BO117" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP117" t="n">
         <v>1000</v>
       </c>
       <c r="BQ117" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR117" t="n">
         <v>1000</v>
       </c>
       <c r="BS117" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT117" t="n">
         <v>1000</v>
       </c>
       <c r="BU117" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV117" t="n">
         <v>1000</v>
       </c>
       <c r="BW117" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX117" t="n">
         <v>1000</v>
       </c>
       <c r="BY117" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ117" t="n">
         <v>1000</v>
       </c>
       <c r="CA117" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB117" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -30345,16 +30345,16 @@
         <v>1.01</v>
       </c>
       <c r="N118" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O118" t="n">
         <v>1.33</v>
       </c>
       <c r="P118" t="n">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="Q118" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R118" t="n">
         <v>1.24</v>
@@ -30486,65 +30486,65 @@
         <v>1000</v>
       </c>
       <c r="BI118" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ118" t="n">
         <v>1000</v>
       </c>
       <c r="BK118" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL118" t="n">
         <v>1000</v>
       </c>
       <c r="BM118" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN118" t="n">
         <v>1000</v>
       </c>
       <c r="BO118" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP118" t="n">
         <v>1000</v>
       </c>
       <c r="BQ118" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR118" t="n">
         <v>1000</v>
       </c>
       <c r="BS118" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT118" t="n">
         <v>1000</v>
       </c>
       <c r="BU118" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV118" t="n">
         <v>1000</v>
       </c>
       <c r="BW118" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX118" t="n">
         <v>1000</v>
       </c>
       <c r="BY118" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ118" t="n">
         <v>1000</v>
       </c>
       <c r="CA118" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB118" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -30608,16 +30608,16 @@
         <v>1.87</v>
       </c>
       <c r="Q119" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="R119" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S119" t="n">
         <v>3.25</v>
       </c>
       <c r="T119" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="U119" t="n">
         <v>1.11</v>
@@ -30798,7 +30798,7 @@
       </c>
       <c r="CB119" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -30841,7 +30841,7 @@
         <v>2.9</v>
       </c>
       <c r="J120" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K120" t="n">
         <v>3.35</v>
@@ -30994,65 +30994,65 @@
         <v>1000</v>
       </c>
       <c r="BI120" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ120" t="n">
         <v>1000</v>
       </c>
       <c r="BK120" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL120" t="n">
         <v>1000</v>
       </c>
       <c r="BM120" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN120" t="n">
         <v>1000</v>
       </c>
       <c r="BO120" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP120" t="n">
         <v>1000</v>
       </c>
       <c r="BQ120" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR120" t="n">
         <v>1000</v>
       </c>
       <c r="BS120" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT120" t="n">
         <v>1000</v>
       </c>
       <c r="BU120" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV120" t="n">
         <v>1000</v>
       </c>
       <c r="BW120" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX120" t="n">
         <v>1000</v>
       </c>
       <c r="BY120" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ120" t="n">
         <v>1000</v>
       </c>
       <c r="CA120" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB120" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -31306,7 +31306,7 @@
       </c>
       <c r="CB121" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -31544,7 +31544,7 @@
         <v>1000</v>
       </c>
       <c r="BW122" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BX122" t="n">
         <v>1000</v>
@@ -31560,7 +31560,7 @@
       </c>
       <c r="CB122" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -31591,10 +31591,10 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G123" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H123" t="n">
         <v>5.1</v>
@@ -31606,7 +31606,7 @@
         <v>3.7</v>
       </c>
       <c r="K123" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L123" t="n">
         <v>1.01</v>
@@ -31615,13 +31615,13 @@
         <v>1.01</v>
       </c>
       <c r="N123" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="O123" t="n">
         <v>1.3</v>
       </c>
       <c r="P123" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="Q123" t="n">
         <v>1.89</v>
@@ -31639,10 +31639,10 @@
         <v>1.11</v>
       </c>
       <c r="V123" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W123" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X123" t="n">
         <v>1000</v>
@@ -31756,65 +31756,65 @@
         <v>1000</v>
       </c>
       <c r="BI123" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ123" t="n">
         <v>1000</v>
       </c>
       <c r="BK123" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL123" t="n">
         <v>1000</v>
       </c>
       <c r="BM123" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN123" t="n">
         <v>1000</v>
       </c>
       <c r="BO123" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP123" t="n">
         <v>1000</v>
       </c>
       <c r="BQ123" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR123" t="n">
         <v>1000</v>
       </c>
       <c r="BS123" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT123" t="n">
         <v>1000</v>
       </c>
       <c r="BU123" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV123" t="n">
         <v>1000</v>
       </c>
       <c r="BW123" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX123" t="n">
         <v>1000</v>
       </c>
       <c r="BY123" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ123" t="n">
         <v>1000</v>
       </c>
       <c r="CA123" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB123" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -31854,37 +31854,37 @@
         <v>4.2</v>
       </c>
       <c r="I124" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J124" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K124" t="n">
         <v>3.9</v>
       </c>
       <c r="L124" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M124" t="n">
         <v>1.05</v>
       </c>
       <c r="N124" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O124" t="n">
         <v>1.26</v>
       </c>
       <c r="P124" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q124" t="n">
         <v>1.79</v>
       </c>
       <c r="R124" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S124" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T124" t="n">
         <v>1.71</v>
@@ -31902,7 +31902,7 @@
         <v>18.5</v>
       </c>
       <c r="Y124" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z124" t="n">
         <v>36</v>
@@ -31914,7 +31914,7 @@
         <v>11.5</v>
       </c>
       <c r="AC124" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD124" t="n">
         <v>17</v>
@@ -31923,22 +31923,22 @@
         <v>55</v>
       </c>
       <c r="AF124" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG124" t="n">
         <v>11</v>
       </c>
       <c r="AH124" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI124" t="n">
         <v>55</v>
       </c>
       <c r="AJ124" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK124" t="n">
         <v>23</v>
-      </c>
-      <c r="AK124" t="n">
-        <v>22</v>
       </c>
       <c r="AL124" t="n">
         <v>34</v>
@@ -32004,25 +32004,25 @@
         <v>10</v>
       </c>
       <c r="BG124" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH124" t="n">
         <v>1000</v>
       </c>
       <c r="BI124" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BJ124" t="n">
         <v>13.5</v>
       </c>
       <c r="BK124" t="n">
-        <v>5.8</v>
+        <v>1.66</v>
       </c>
       <c r="BL124" t="n">
         <v>1000</v>
       </c>
       <c r="BM124" t="n">
-        <v>21</v>
+        <v>1.89</v>
       </c>
       <c r="BN124" t="n">
         <v>6.6</v>
@@ -32034,13 +32034,13 @@
         <v>19</v>
       </c>
       <c r="BQ124" t="n">
-        <v>8</v>
+        <v>1.72</v>
       </c>
       <c r="BR124" t="n">
         <v>36</v>
       </c>
       <c r="BS124" t="n">
-        <v>15</v>
+        <v>1.8</v>
       </c>
       <c r="BT124" t="n">
         <v>11</v>
@@ -32052,23 +32052,23 @@
         <v>48</v>
       </c>
       <c r="BW124" t="n">
-        <v>19</v>
+        <v>1.82</v>
       </c>
       <c r="BX124" t="n">
         <v>1000</v>
       </c>
       <c r="BY124" t="n">
-        <v>21</v>
+        <v>1.83</v>
       </c>
       <c r="BZ124" t="n">
         <v>29</v>
       </c>
       <c r="CA124" t="n">
-        <v>12</v>
+        <v>1.77</v>
       </c>
       <c r="CB124" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -32126,7 +32126,7 @@
         <v>2.64</v>
       </c>
       <c r="O125" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P125" t="n">
         <v>1.66</v>
@@ -32264,19 +32264,19 @@
         <v>1000</v>
       </c>
       <c r="BI125" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BJ125" t="n">
         <v>14.5</v>
       </c>
       <c r="BK125" t="n">
-        <v>6.8</v>
+        <v>1.61</v>
       </c>
       <c r="BL125" t="n">
         <v>1000</v>
       </c>
       <c r="BM125" t="n">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="BN125" t="n">
         <v>6.6</v>
@@ -32288,13 +32288,13 @@
         <v>26</v>
       </c>
       <c r="BQ125" t="n">
-        <v>12</v>
+        <v>1.69</v>
       </c>
       <c r="BR125" t="n">
         <v>50</v>
       </c>
       <c r="BS125" t="n">
-        <v>21</v>
+        <v>1.74</v>
       </c>
       <c r="BT125" t="n">
         <v>9</v>
@@ -32306,23 +32306,23 @@
         <v>46</v>
       </c>
       <c r="BW125" t="n">
-        <v>20</v>
+        <v>1.74</v>
       </c>
       <c r="BX125" t="n">
         <v>1000</v>
       </c>
       <c r="BY125" t="n">
-        <v>21</v>
+        <v>1.76</v>
       </c>
       <c r="BZ125" t="n">
         <v>50</v>
       </c>
       <c r="CA125" t="n">
-        <v>21</v>
+        <v>1.74</v>
       </c>
       <c r="CB125" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -32353,10 +32353,10 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G126" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H126" t="n">
         <v>4.1</v>
@@ -32371,28 +32371,28 @@
         <v>3.95</v>
       </c>
       <c r="L126" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M126" t="n">
         <v>1.06</v>
       </c>
       <c r="N126" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O126" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P126" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q126" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R126" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S126" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="T126" t="n">
         <v>1.72</v>
@@ -32401,16 +32401,16 @@
         <v>2.2</v>
       </c>
       <c r="V126" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W126" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X126" t="n">
         <v>19.5</v>
       </c>
       <c r="Y126" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z126" t="n">
         <v>40</v>
@@ -32437,7 +32437,7 @@
         <v>12.5</v>
       </c>
       <c r="AH126" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI126" t="n">
         <v>65</v>
@@ -32470,7 +32470,7 @@
         <v>4.8</v>
       </c>
       <c r="AS126" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT126" t="n">
         <v>9.199999999999999</v>
@@ -32494,7 +32494,7 @@
         <v>14.5</v>
       </c>
       <c r="BA126" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB126" t="n">
         <v>20</v>
@@ -32506,31 +32506,31 @@
         <v>4.7</v>
       </c>
       <c r="BE126" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF126" t="n">
         <v>9.4</v>
       </c>
       <c r="BG126" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH126" t="n">
         <v>1000</v>
       </c>
       <c r="BI126" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BJ126" t="n">
         <v>13</v>
       </c>
       <c r="BK126" t="n">
-        <v>6.2</v>
+        <v>1.69</v>
       </c>
       <c r="BL126" t="n">
         <v>1000</v>
       </c>
       <c r="BM126" t="n">
-        <v>21</v>
+        <v>1.94</v>
       </c>
       <c r="BN126" t="n">
         <v>6.4</v>
@@ -32542,13 +32542,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ126" t="n">
-        <v>8.4</v>
+        <v>1.76</v>
       </c>
       <c r="BR126" t="n">
         <v>36</v>
       </c>
       <c r="BS126" t="n">
-        <v>16</v>
+        <v>1.84</v>
       </c>
       <c r="BT126" t="n">
         <v>10.5</v>
@@ -32560,23 +32560,23 @@
         <v>46</v>
       </c>
       <c r="BW126" t="n">
-        <v>21</v>
+        <v>1.86</v>
       </c>
       <c r="BX126" t="n">
         <v>1000</v>
       </c>
       <c r="BY126" t="n">
-        <v>21</v>
+        <v>1.88</v>
       </c>
       <c r="BZ126" t="n">
         <v>29</v>
       </c>
       <c r="CA126" t="n">
-        <v>13</v>
+        <v>1.82</v>
       </c>
       <c r="CB126" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -32610,10 +32610,10 @@
         <v>1.64</v>
       </c>
       <c r="G127" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="H127" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I127" t="n">
         <v>5.1</v>
@@ -32622,31 +32622,31 @@
         <v>4.8</v>
       </c>
       <c r="K127" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="L127" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M127" t="n">
         <v>1.01</v>
       </c>
       <c r="N127" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="O127" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P127" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="Q127" t="n">
         <v>1.31</v>
       </c>
       <c r="R127" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S127" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="T127" t="n">
         <v>1.35</v>
@@ -32658,7 +32658,7 @@
         <v>1.24</v>
       </c>
       <c r="W127" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="X127" t="n">
         <v>60</v>
@@ -32772,7 +32772,7 @@
         <v>1000</v>
       </c>
       <c r="BI127" t="n">
-        <v>4.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ127" t="n">
         <v>12.5</v>
@@ -32784,7 +32784,7 @@
         <v>1000</v>
       </c>
       <c r="BM127" t="n">
-        <v>21</v>
+        <v>2.08</v>
       </c>
       <c r="BN127" t="n">
         <v>7.8</v>
@@ -32796,31 +32796,31 @@
         <v>14.5</v>
       </c>
       <c r="BQ127" t="n">
-        <v>6.2</v>
+        <v>1.87</v>
       </c>
       <c r="BR127" t="n">
         <v>23</v>
       </c>
       <c r="BS127" t="n">
-        <v>9.6</v>
+        <v>1.97</v>
       </c>
       <c r="BT127" t="n">
         <v>13.5</v>
       </c>
       <c r="BU127" t="n">
-        <v>5.9</v>
+        <v>1.86</v>
       </c>
       <c r="BV127" t="n">
         <v>44</v>
       </c>
       <c r="BW127" t="n">
-        <v>16.5</v>
+        <v>2.04</v>
       </c>
       <c r="BX127" t="n">
         <v>40</v>
       </c>
       <c r="BY127" t="n">
-        <v>16</v>
+        <v>2.04</v>
       </c>
       <c r="BZ127" t="n">
         <v>12.5</v>
@@ -32830,7 +32830,7 @@
       </c>
       <c r="CB127" t="inlineStr">
         <is>
-          <t>2026-05-21 21:43:59</t>
+          <t>2026-05-22 00:11:37</t>
         </is>
       </c>
     </row>
